--- a/currentbuild/StructureDefinition-mal-observation-blodprove.xlsx
+++ b/currentbuild/StructureDefinition-mal-observation-blodprove.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.1</t>
+    <t>1.3.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-mal-observation-blodprove.xlsx
+++ b/currentbuild/StructureDefinition-mal-observation-blodprove.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-mal-observation-blodprove.xlsx
+++ b/currentbuild/StructureDefinition-mal-observation-blodprove.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2594" uniqueCount="490">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.1</t>
+    <t>1.4.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -798,7 +798,7 @@
 </t>
   </si>
   <si>
-    <t>open</t>
+    <t>closed</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -823,13 +823,39 @@
 </t>
   </si>
   <si>
-    <t>Observation.issued</t>
+    <t>Observation.effective[x]:effectivePeriod</t>
+  </si>
+  <si>
+    <t>effectivePeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]:effectiveTiming</t>
+  </si>
+  <si>
+    <t>effectiveTiming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timing
+</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]:effectiveInstant</t>
+  </si>
+  <si>
+    <t>effectiveInstant</t>
   </si>
   <si>
     <t xml:space="preserve">instant
 </t>
   </si>
   <si>
+    <t>Observation.issued</t>
+  </si>
+  <si>
     <t>Date/Time this version was made available</t>
   </si>
   <si>
@@ -921,6 +947,94 @@
 </t>
   </si>
   <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueBoolean</t>
+  </si>
+  <si>
+    <t>valueBoolean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueInteger</t>
+  </si>
+  <si>
+    <t>valueInteger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueRange</t>
+  </si>
+  <si>
+    <t>valueRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueRatio</t>
+  </si>
+  <si>
+    <t>valueRatio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueSampledData</t>
+  </si>
+  <si>
+    <t>valueSampledData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SampledData
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueTime</t>
+  </si>
+  <si>
+    <t>valueTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueDateTime</t>
+  </si>
+  <si>
+    <t>valueDateTime</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valuePeriod</t>
+  </si>
+  <si>
+    <t>valuePeriod</t>
+  </si>
+  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -1161,10 +1275,6 @@
     <t>Observation.referenceRange.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -1218,6 +1328,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -1293,10 +1407,6 @@
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range
-</t>
   </si>
   <si>
     <t>Applicable age range, if relevant</t>
@@ -1761,12 +1871,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP53"/>
+  <dimension ref="A1:AP66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.40234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -4354,11 +4464,13 @@
         <v>258</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="D22" t="s" s="2">
-        <v>82</v>
+        <v>243</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4377,18 +4489,20 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4436,7 +4550,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4451,19 +4565,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4471,21 +4585,23 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>243</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4497,17 +4613,19 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="O23" t="s" s="2">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4556,13 +4674,13 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
@@ -4571,19 +4689,19 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4591,14 +4709,16 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>243</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4617,19 +4737,19 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>279</v>
+        <v>247</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4666,17 +4786,19 @@
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AC24" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4685,40 +4807,38 @@
         <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>283</v>
+        <v>252</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>284</v>
+        <v>253</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>285</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4730,7 +4850,7 @@
         <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>82</v>
@@ -4739,20 +4859,18 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4800,7 +4918,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4809,7 +4927,7 @@
         <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>105</v>
@@ -4818,27 +4936,27 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>285</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4849,7 +4967,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -4858,22 +4976,20 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>275</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4898,13 +5014,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -4922,34 +5038,34 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>136</v>
+        <v>280</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -4957,21 +5073,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -4980,22 +5096,22 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>191</v>
+        <v>284</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5020,40 +5136,38 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>105</v>
@@ -5062,29 +5176,31 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>310</v>
+        <v>293</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5093,31 +5209,31 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>313</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5166,16 +5282,16 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>105</v>
@@ -5184,29 +5300,31 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5224,21 +5342,23 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>321</v>
+        <v>286</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5262,13 +5382,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5286,7 +5406,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>319</v>
+        <v>283</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5295,7 +5415,7 @@
         <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>105</v>
@@ -5304,29 +5424,31 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>326</v>
+        <v>291</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>327</v>
+        <v>292</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>328</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>329</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5344,22 +5466,22 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>191</v>
+        <v>301</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>330</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>331</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>332</v>
+        <v>287</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>333</v>
+        <v>288</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5384,13 +5506,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5408,7 +5530,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>329</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5417,7 +5539,7 @@
         <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>105</v>
@@ -5426,29 +5548,31 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>336</v>
+        <v>291</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>337</v>
+        <v>292</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>338</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5466,21 +5590,23 @@
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>339</v>
+        <v>304</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>340</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>341</v>
+        <v>286</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5528,7 +5654,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>338</v>
+        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5537,7 +5663,7 @@
         <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>105</v>
@@ -5546,29 +5672,31 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>343</v>
+        <v>290</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>344</v>
+        <v>291</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>345</v>
+        <v>292</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>346</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>347</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="D32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5586,21 +5714,23 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>348</v>
+        <v>307</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>350</v>
+        <v>286</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5648,7 +5778,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>347</v>
+        <v>283</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5657,7 +5787,7 @@
         <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>105</v>
@@ -5666,29 +5796,31 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>352</v>
+        <v>290</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>353</v>
+        <v>291</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>354</v>
+        <v>292</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>355</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>356</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="D33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5697,7 +5829,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5706,22 +5838,22 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>357</v>
+        <v>310</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>358</v>
+        <v>285</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>359</v>
+        <v>286</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>360</v>
+        <v>287</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>361</v>
+        <v>288</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5770,47 +5902,49 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>356</v>
+        <v>283</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>362</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>363</v>
+        <v>291</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>364</v>
+        <v>292</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>365</v>
+        <v>311</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>82</v>
       </c>
@@ -5828,19 +5962,23 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>366</v>
+        <v>313</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>367</v>
+        <v>285</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -5888,7 +6026,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>369</v>
+        <v>283</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5897,47 +6035,49 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>370</v>
+        <v>292</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>371</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="D35" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -5946,21 +6086,23 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>139</v>
+        <v>316</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>140</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>372</v>
+        <v>286</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6008,80 +6150,82 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>373</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>370</v>
+        <v>292</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>374</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="D36" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>139</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>376</v>
+        <v>285</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>377</v>
+        <v>286</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>142</v>
+        <v>287</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>148</v>
+        <v>288</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6130,47 +6274,49 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>378</v>
+        <v>283</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>136</v>
+        <v>292</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>379</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="D37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6188,19 +6334,23 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>380</v>
+        <v>257</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>381</v>
+        <v>285</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6248,7 +6398,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>379</v>
+        <v>283</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6257,7 +6407,7 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>383</v>
+        <v>289</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -6266,29 +6416,31 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>384</v>
+        <v>291</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>385</v>
+        <v>292</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>386</v>
+        <v>322</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6306,19 +6458,23 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>387</v>
+        <v>285</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6366,7 +6522,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>386</v>
+        <v>283</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6375,7 +6531,7 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>383</v>
+        <v>289</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>105</v>
@@ -6384,27 +6540,27 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>384</v>
+        <v>291</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>389</v>
+        <v>292</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>390</v>
+        <v>324</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>390</v>
+        <v>324</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6430,16 +6586,16 @@
         <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>391</v>
+        <v>325</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>392</v>
+        <v>326</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>393</v>
+        <v>327</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>394</v>
+        <v>328</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6464,13 +6620,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>117</v>
+        <v>329</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>395</v>
+        <v>330</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>396</v>
+        <v>331</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6488,7 +6644,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>390</v>
+        <v>324</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6497,7 +6653,7 @@
         <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>105</v>
@@ -6506,13 +6662,13 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>398</v>
+        <v>136</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6523,14 +6679,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>334</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>334</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6552,16 +6708,16 @@
         <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>400</v>
+        <v>336</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
+        <v>337</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>402</v>
+        <v>338</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>403</v>
+        <v>339</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6586,13 +6742,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>206</v>
+        <v>329</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>404</v>
+        <v>340</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>405</v>
+        <v>341</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6610,7 +6766,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>399</v>
+        <v>334</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6628,27 +6784,27 @@
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>397</v>
+        <v>342</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>398</v>
+        <v>343</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>309</v>
+        <v>344</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>406</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>406</v>
+        <v>346</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6659,7 +6815,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6671,17 +6827,19 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>407</v>
+        <v>347</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>408</v>
+        <v>348</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O41" t="s" s="2">
-        <v>410</v>
+        <v>351</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6730,13 +6888,13 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>406</v>
+        <v>346</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
@@ -6751,10 +6909,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>411</v>
+        <v>353</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6765,10 +6923,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>412</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
+        <v>354</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6791,15 +6949,17 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>366</v>
+        <v>191</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>413</v>
+        <v>355</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6824,13 +6984,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -6848,7 +7008,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>412</v>
+        <v>354</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6866,27 +7026,27 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>415</v>
+        <v>362</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>416</v>
+        <v>364</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>416</v>
+        <v>364</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6897,7 +7057,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -6906,21 +7066,23 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>417</v>
+        <v>191</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>418</v>
+        <v>365</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>419</v>
+        <v>366</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -6944,13 +7106,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -6968,13 +7130,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>416</v>
+        <v>364</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -6989,10 +7151,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>421</v>
+        <v>371</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>422</v>
+        <v>372</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7003,10 +7165,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>423</v>
+        <v>373</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>423</v>
+        <v>373</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7017,7 +7179,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7026,19 +7188,19 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>424</v>
+        <v>374</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>425</v>
+        <v>375</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>426</v>
+        <v>376</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>427</v>
+        <v>377</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7088,13 +7250,13 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>423</v>
+        <v>373</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
@@ -7106,27 +7268,27 @@
         <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>421</v>
+        <v>379</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>428</v>
+        <v>380</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>82</v>
+        <v>381</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>429</v>
+        <v>382</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>429</v>
+        <v>382</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7137,7 +7299,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7146,23 +7308,21 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>430</v>
+        <v>384</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>431</v>
+        <v>385</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7210,13 +7370,13 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>429</v>
+        <v>382</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
@@ -7228,27 +7388,27 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>434</v>
+        <v>388</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>435</v>
+        <v>389</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>391</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>391</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7259,7 +7419,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7271,16 +7431,20 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7328,19 +7492,19 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7349,10 +7513,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7363,21 +7527,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>437</v>
+        <v>400</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>437</v>
+        <v>400</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7389,17 +7553,15 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>139</v>
+        <v>301</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>140</v>
+        <v>401</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7448,19 +7610,19 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>373</v>
+        <v>403</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7472,7 +7634,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7483,14 +7645,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>438</v>
+        <v>405</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>438</v>
+        <v>405</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>375</v>
+        <v>138</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7503,26 +7665,24 @@
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>140</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
+        <v>406</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="O48" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7570,7 +7730,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7594,7 +7754,7 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>136</v>
+        <v>404</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7605,45 +7765,45 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>439</v>
+        <v>408</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>439</v>
+        <v>408</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>441</v>
+        <v>411</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>442</v>
+        <v>142</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>205</v>
+        <v>148</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7668,13 +7828,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7692,34 +7852,34 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>439</v>
+        <v>412</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>212</v>
+        <v>136</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7727,10 +7887,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7750,23 +7910,19 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>276</v>
+        <v>414</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>445</v>
+        <v>415</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -7814,7 +7970,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7823,36 +7979,36 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>105</v>
+        <v>418</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>283</v>
+        <v>419</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>284</v>
+        <v>420</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>285</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7875,20 +8031,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>191</v>
+        <v>414</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>449</v>
+        <v>422</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -7912,13 +8064,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -7936,7 +8088,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7945,10 +8097,10 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>297</v>
+        <v>417</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>418</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -7957,10 +8109,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>136</v>
+        <v>419</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>298</v>
+        <v>424</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -7971,21 +8123,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8000,16 +8152,16 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>301</v>
+        <v>426</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>302</v>
+        <v>427</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>303</v>
+        <v>428</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>304</v>
+        <v>429</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8034,13 +8186,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>294</v>
+        <v>117</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>305</v>
+        <v>430</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>306</v>
+        <v>431</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8058,13 +8210,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8076,27 +8228,27 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>307</v>
+        <v>432</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>308</v>
+        <v>433</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>309</v>
+        <v>344</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8119,19 +8271,19 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>83</v>
+        <v>191</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>455</v>
+        <v>436</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>360</v>
+        <v>437</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>361</v>
+        <v>438</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8156,13 +8308,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8180,7 +8332,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8198,23 +8350,1593 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>363</v>
+        <v>433</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP53">
+  <autoFilter ref="A1:AP66">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8224,7 +9946,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI52">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/currentbuild/StructureDefinition-mal-observation-blodprove.xlsx
+++ b/currentbuild/StructureDefinition-mal-observation-blodprove.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.2</t>
+    <t>1.4.3</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-mal-observation-blodprove.xlsx
+++ b/currentbuild/StructureDefinition-mal-observation-blodprove.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.3</t>
+    <t>1.4.4</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-mal-observation-blodprove.xlsx
+++ b/currentbuild/StructureDefinition-mal-observation-blodprove.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.5</t>
+    <t>1.4.6</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-mal-observation-blodprove.xlsx
+++ b/currentbuild/StructureDefinition-mal-observation-blodprove.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.6</t>
+    <t>1.4.7</t>
   </si>
   <si>
     <t>Name</t>
